--- a/site/HR-to-Microsoft-Directory-Active-Directory-Entra-ID-Integration-Template-Version-History/headings.xlsx
+++ b/site/HR-to-Microsoft-Directory-Active-Directory-Entra-ID-Integration-Template-Version-History/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,28 +479,6 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Active-Directory-Entra-ID-Integration-Template-Version-History/#h_01KH8AAX7AFMQZCC316FTNS9Z0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>h_01KY6TA4BT47DM8ZRYHF3GQ8TC</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Microsoft-Directory-Active-Directory-Entra-ID-Integration-Template-Version-History/#h_01KY6TA4BT47DM8ZRYHF3GQ8TC</t>
         </is>
       </c>
     </row>
